--- a/FINAL450.xlsx
+++ b/FINAL450.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saptarshi mondal\Desktop\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F16024-AD5B-4077-BF7E-8FED89F443A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F989AE0-E94B-44D3-A25B-6DAF7C9225D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{261C335C-1D91-C143-AEEF-19B82073468C}"/>
   </bookViews>
@@ -5713,7 +5713,7 @@
         <v>343</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="361" spans="1:3" ht="21">
@@ -5724,7 +5724,7 @@
         <v>344</v>
       </c>
       <c r="C361" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="362" spans="1:3" ht="21">
@@ -5735,7 +5735,7 @@
         <v>345</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="363" spans="1:3" ht="21">
@@ -5746,7 +5746,7 @@
         <v>346</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="21">
@@ -5757,7 +5757,7 @@
         <v>347</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="365" spans="1:3" ht="21">
@@ -5768,7 +5768,7 @@
         <v>348</v>
       </c>
       <c r="C365" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="366" spans="1:3" ht="21">
@@ -5779,7 +5779,7 @@
         <v>349</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="367" spans="1:3" ht="21">
@@ -5790,7 +5790,7 @@
         <v>350</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="21">
@@ -5801,7 +5801,7 @@
         <v>351</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="369" spans="1:3" ht="21">
@@ -5812,7 +5812,7 @@
         <v>352</v>
       </c>
       <c r="C369" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="370" spans="1:3" ht="21">
@@ -5823,7 +5823,7 @@
         <v>353</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="371" spans="1:3" ht="21">
@@ -5834,7 +5834,7 @@
         <v>354</v>
       </c>
       <c r="C371" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="372" spans="1:3" ht="21">
@@ -5845,7 +5845,7 @@
         <v>355</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="373" spans="1:3" ht="21">
@@ -5867,7 +5867,7 @@
         <v>357</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="375" spans="1:3" ht="21">
@@ -5878,7 +5878,7 @@
         <v>358</v>
       </c>
       <c r="C375" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="376" spans="1:3" ht="21">
@@ -5889,7 +5889,7 @@
         <v>359</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="21">
@@ -5900,7 +5900,7 @@
         <v>360</v>
       </c>
       <c r="C377" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="378" spans="1:3" ht="21">
@@ -5911,7 +5911,7 @@
         <v>361</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="379" spans="1:3" ht="21">
@@ -5933,7 +5933,7 @@
         <v>363</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="381" spans="1:3" ht="21">
@@ -5944,7 +5944,7 @@
         <v>364</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="382" spans="1:3" ht="21">

--- a/FINAL450.xlsx
+++ b/FINAL450.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saptarshi mondal\Desktop\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F989AE0-E94B-44D3-A25B-6DAF7C9225D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F937DE4-969A-494F-9557-8D2D78DC46A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{261C335C-1D91-C143-AEEF-19B82073468C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="470">
   <si>
     <t>Questions by Love Babbar:</t>
   </si>
@@ -1432,13 +1432,16 @@
   </si>
   <si>
     <t>NO</t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1521,6 +1524,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1564,11 +1574,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyFill="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1606,13 +1619,14 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Input" xfId="3" builtinId="20"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Style 1" xfId="4" xr:uid="{EB6A0C06-EC0A-4508-95C8-887271625051}"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1620,6 +1634,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5856,7 +5877,7 @@
         <v>356</v>
       </c>
       <c r="C373" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="21">
@@ -5922,7 +5943,7 @@
         <v>362</v>
       </c>
       <c r="C379" s="4" t="s">
-        <v>4</v>
+        <v>469</v>
       </c>
     </row>
     <row r="380" spans="1:3" ht="21">
@@ -5955,7 +5976,7 @@
         <v>365</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="383" spans="1:3" ht="21">
@@ -5966,7 +5987,7 @@
         <v>366</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="384" spans="1:3" ht="21">
@@ -5977,7 +5998,7 @@
         <v>367</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="21">
@@ -5988,7 +6009,7 @@
         <v>368</v>
       </c>
       <c r="C385" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="21">
@@ -5999,7 +6020,7 @@
         <v>369</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="21">
@@ -6010,7 +6031,7 @@
         <v>370</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="388" spans="1:3" ht="21">
@@ -6021,7 +6042,7 @@
         <v>371</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="21">
@@ -6032,7 +6053,7 @@
         <v>372</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="21">
@@ -6043,7 +6064,7 @@
         <v>373</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="21">
@@ -6054,7 +6075,7 @@
         <v>374</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="21">
@@ -6065,7 +6086,7 @@
         <v>375</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>4</v>
+        <v>469</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="21">
@@ -6076,7 +6097,7 @@
         <v>376</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>4</v>
+        <v>469</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="21">
@@ -6087,7 +6108,7 @@
         <v>376</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>4</v>
+        <v>469</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="21">
@@ -6098,7 +6119,7 @@
         <v>377</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="21">
@@ -6109,7 +6130,7 @@
         <v>378</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>4</v>
+        <v>469</v>
       </c>
     </row>
     <row r="397" spans="1:3" ht="21">
@@ -6120,7 +6141,7 @@
         <v>379</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="398" spans="1:3" ht="21">
@@ -6131,7 +6152,7 @@
         <v>380</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>4</v>
+        <v>469</v>
       </c>
     </row>
     <row r="399" spans="1:3" ht="21">
@@ -6142,7 +6163,7 @@
         <v>381</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>4</v>
+        <v>469</v>
       </c>
     </row>
     <row r="400" spans="1:3" ht="21">
@@ -6153,7 +6174,7 @@
         <v>382</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>4</v>
+        <v>469</v>
       </c>
     </row>
     <row r="401" spans="1:3" ht="21">
@@ -6164,7 +6185,7 @@
         <v>383</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="402" spans="1:3" ht="21">
@@ -6175,7 +6196,7 @@
         <v>384</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>4</v>
+        <v>469</v>
       </c>
     </row>
     <row r="403" spans="1:3" ht="21">
@@ -6186,7 +6207,7 @@
         <v>385</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>4</v>
+        <v>469</v>
       </c>
     </row>
     <row r="404" spans="1:3" ht="21">
@@ -7052,12 +7073,15 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A6:C54">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="yes">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="yes">
       <formula>NOT(ISERROR(SEARCH("yes",A6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="yes">
+    <cfRule type="beginsWith" dxfId="1" priority="1" operator="beginsWith" text="no">
+      <formula>LEFT(A1,LEN("no"))="no"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="yes">
       <formula>NOT(ISERROR(SEARCH("yes",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/FINAL450.xlsx
+++ b/FINAL450.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saptarshi mondal\Desktop\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F937DE4-969A-494F-9557-8D2D78DC46A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA058E66-346F-48DF-8BF5-395EF271EE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{261C335C-1D91-C143-AEEF-19B82073468C}"/>
   </bookViews>
@@ -3820,7 +3820,7 @@
         <v>172</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="21">
@@ -3831,7 +3831,7 @@
         <v>173</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="21">
@@ -3842,7 +3842,7 @@
         <v>174</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="21">
@@ -3853,7 +3853,7 @@
         <v>175</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="21">
@@ -3875,7 +3875,7 @@
         <v>177</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="21">
@@ -3886,7 +3886,7 @@
         <v>178</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="21">
@@ -3897,7 +3897,7 @@
         <v>179</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="21">
@@ -3908,7 +3908,7 @@
         <v>180</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="21">
@@ -3919,7 +3919,7 @@
         <v>181</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="21">
@@ -3930,7 +3930,7 @@
         <v>182</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="21">
@@ -3941,7 +3941,7 @@
         <v>183</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="21">
@@ -3952,7 +3952,7 @@
         <v>184</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="21">
@@ -3963,7 +3963,7 @@
         <v>185</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="21">
@@ -3985,7 +3985,7 @@
         <v>187</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="21">
@@ -4018,7 +4018,7 @@
         <v>190</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="21">
@@ -4029,7 +4029,7 @@
         <v>191</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="21">
@@ -4051,7 +4051,7 @@
         <v>193</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="21">
@@ -4062,7 +4062,7 @@
         <v>194</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="21">
@@ -4084,7 +4084,7 @@
         <v>196</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="21">
@@ -4095,7 +4095,7 @@
         <v>197</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="21">
@@ -4117,7 +4117,7 @@
         <v>199</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="21">
@@ -4139,7 +4139,7 @@
         <v>201</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="21">
@@ -4150,7 +4150,7 @@
         <v>202</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="21">
@@ -4161,7 +4161,7 @@
         <v>203</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="21">
@@ -4215,7 +4215,7 @@
         <v>208</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="21">
@@ -4226,7 +4226,7 @@
         <v>209</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="21">
@@ -4237,7 +4237,7 @@
         <v>210</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="21">
@@ -4248,7 +4248,7 @@
         <v>211</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="21">
@@ -4259,7 +4259,7 @@
         <v>212</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="21">
@@ -4281,7 +4281,7 @@
         <v>214</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="21">
@@ -4292,7 +4292,7 @@
         <v>215</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="21">
@@ -4303,7 +4303,7 @@
         <v>216</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="21">
@@ -4314,7 +4314,7 @@
         <v>217</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="21">
@@ -4325,7 +4325,7 @@
         <v>218</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="21">
@@ -4336,7 +4336,7 @@
         <v>219</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="21">
@@ -4347,7 +4347,7 @@
         <v>220</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="21">
@@ -4358,7 +4358,7 @@
         <v>221</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="21">
@@ -4380,7 +4380,7 @@
         <v>223</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="21">
@@ -4413,7 +4413,7 @@
         <v>226</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="21">
@@ -4424,7 +4424,7 @@
         <v>227</v>
       </c>
       <c r="C233" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="21">
@@ -4435,7 +4435,7 @@
         <v>228</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="21">
@@ -4446,7 +4446,7 @@
         <v>229</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="21">

--- a/FINAL450.xlsx
+++ b/FINAL450.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saptarshi mondal\Desktop\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA058E66-346F-48DF-8BF5-395EF271EE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2FD4CE-60DC-498C-95FC-5C26A29B3D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{261C335C-1D91-C143-AEEF-19B82073468C}"/>
   </bookViews>
@@ -5528,7 +5528,7 @@
         <v>324</v>
       </c>
       <c r="C340" s="4" t="s">
-        <v>4</v>
+        <v>464</v>
       </c>
     </row>
     <row r="341" spans="1:3" ht="21">
